--- a/#SosCuba_anonymized.xlsx
+++ b/#SosCuba_anonymized.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -9700,7 +9700,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9744,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9956,7 +9956,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>正面</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10041,7 +10041,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10085,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10128,7 +10128,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10178,7 +10178,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10220,7 +10220,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10388,7 +10388,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10558,7 +10558,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -24428,7 +24428,7 @@
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -29089,7 +29089,7 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29131,7 +29131,7 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29175,7 +29175,7 @@
       </c>
       <c r="J849" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29220,7 +29220,7 @@
       </c>
       <c r="J850" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29263,7 +29263,7 @@
       </c>
       <c r="J851" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -29307,7 +29307,7 @@
       </c>
       <c r="J852" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29350,7 +29350,7 @@
       </c>
       <c r="J853" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -29399,7 +29399,7 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
@@ -29442,7 +29442,7 @@
       </c>
       <c r="J855" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -29484,7 +29484,7 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>负面</t>
+          <t>negative</t>
         </is>
       </c>
     </row>
